--- a/giro_da_praça_ofertas - SEXTA.xlsx
+++ b/giro_da_praça_ofertas - SEXTA.xlsx
@@ -1,31 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F0EB7F-704B-4D9E-848E-89221056326A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EED47F6-D8CE-4BD0-B5D1-75ED4E96E734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="52">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -142,6 +138,45 @@
   </si>
   <si>
     <t>LINGUIÇA CASEIRA BOVINA KG</t>
+  </si>
+  <si>
+    <t>7896227690017 creme para assaduras cottonbaby 45g snoop R$12,99</t>
+  </si>
+  <si>
+    <t>7896018750807 shampoo infantil huggies kids 360ml cachinho poder R$13,99</t>
+  </si>
+  <si>
+    <t>7891010030094 shampoo johnsons babe 200ml ph balanceada R$17,99</t>
+  </si>
+  <si>
+    <t>7896331100372 doce de leite aviação pote 400g tradicional R$13,99</t>
+  </si>
+  <si>
+    <t>7891110071935 doce de leite mu-mu pote 350g chocolate R$11,99</t>
+  </si>
+  <si>
+    <t>7896045114313 canjica dona clara 400g branca mugunza  R$3,99</t>
+  </si>
+  <si>
+    <t>7892300002661 azeite de oliva sinhá 250ml belo porto  R$20,99</t>
+  </si>
+  <si>
+    <t>7896045110667 bebida lactea 3 corações 250ml power whey chocolate R$6,99</t>
+  </si>
+  <si>
+    <t>7896292303614 molho salada predilecta 235ml parmesan  R$5,99</t>
+  </si>
+  <si>
+    <t>7898080643261 bebida lactea italac 200ml light chocolate  R$1,69</t>
+  </si>
+  <si>
+    <t>7896049502604 desodorante herbissimo 150g mentos fruit  R$8,99</t>
+  </si>
+  <si>
+    <t>7891010253707 sabonete liquido johnsons 400ml limpeza super R$36,99</t>
+  </si>
+  <si>
+    <t>7891010035976 sabonete johnsons 80g mel e vitamina e  R$5,99</t>
   </si>
 </sst>
 </file>
@@ -151,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,28 +199,27 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -229,30 +263,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,17 +597,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="30.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="30.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,416 +621,495 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>320013</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>2.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>130293</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>306946</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>246975</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>150940</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>206159</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>111324</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>111565</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>108785</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>298984</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>320121</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>105461</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>105456</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>105463</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>105449</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>105435</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>107260</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>30.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>106053</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>105062</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>106034</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>106032</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>305039</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEXTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE901A9-D72F-4425-868A-DB33E46B6567}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="70.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEXTA.xlsx
+++ b/giro_da_praça_ofertas - SEXTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA20F0F-CA0C-4B1C-8AA7-208DD46367AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7D9892-7ED4-4494-9FA6-2CC575C35C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -549,6 +549,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -995,6 +998,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SEXTA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEXTA.xlsx
+++ b/giro_da_praça_ofertas - SEXTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7D9892-7ED4-4494-9FA6-2CC575C35C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44108550-D7E9-42D1-9C31-3423D59D3710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -145,7 +140,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,21 +160,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -223,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -231,22 +236,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,447 +562,447 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="32.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>105470</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>105461</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>105457</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>105449</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>105474</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>33.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>107260</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>32.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>115278</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>106053</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>105062</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>106052</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>287263</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>341330</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>294636</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>26.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>111565</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>108785</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>108856</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>108786</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>109388</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>14.49</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>195365</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>304309</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>146797</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>146785</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>119916</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>13.49</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SEXTA.xlsx
+++ b/giro_da_praça_ofertas - SEXTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F506B239-39AE-4873-9B21-A51084A0E1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCB173A-E050-4BB3-A623-11D9CA864690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -100,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,21 +115,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -178,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -186,22 +191,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,249 +517,249 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="33.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>157014</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>158997</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>105461</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>239334</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>105468</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>105458</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>105471</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>105449</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>105435</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>106053</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>106052</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>305039</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SEXTA.xlsx
+++ b/giro_da_praça_ofertas - SEXTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47960591-675A-4091-86C0-EEDEEF0D247B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC79EB3C-4B90-43EA-9494-D5DAF6C47000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,6 +40,69 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
+    <t>QUARTA A SABADO - PERECIVEIS 09 A 12/09/26 MATRIZ</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+  </si>
+  <si>
+    <t>BATATAS CONGELADAS SADIA PCT 400G PALITO PRE-FRITA</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+  </si>
+  <si>
+    <t>MANTEIGA DE COCO PUROCOCO OHANA 200G</t>
+  </si>
+  <si>
+    <t>MANTEIGA QUEIJOLEITE 200G PRIMEIRA QUALIDADE</t>
+  </si>
+  <si>
+    <t>MARGARINA DELINE 500G COM SAL</t>
+  </si>
+  <si>
+    <t>MARGARINA VIGOR 77% 250G COM SAL SABOR MANTEIGA</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
+  </si>
+  <si>
+    <t>QUEIJO MUSSARELA BOUA 150G FATIADA</t>
+  </si>
+  <si>
+    <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - PÃES E BOLOS</t>
+  </si>
+  <si>
+    <t>PÃO DE ALHO DI NAPOLI 350G QUEIJO E ERVAS</t>
+  </si>
+  <si>
+    <t>#03 AÇOUGUE - #01 AVES</t>
+  </si>
+  <si>
+    <t>CORAÇÃO DE FRANGO BONASA BDJ 1KG</t>
+  </si>
+  <si>
+    <t>FILE DE PEITO DE FRANGO SEARA PCT 1KG</t>
+  </si>
+  <si>
+    <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
+  </si>
+  <si>
+    <t>FILEZINHO DE PEITO DE FRANGO SEARA 1KG</t>
+  </si>
+  <si>
+    <t>FILÉ DE PEITO DE FRANGO SADIA BDJ 1KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
+  </si>
+  <si>
+    <t>PEITO DE FRANGO SADIA 1KG A PASSARINHO</t>
+  </si>
+  <si>
     <t>SEXTA - ACOUGUE 11/09/26 MATRIZ</t>
   </si>
   <si>
@@ -68,6 +131,33 @@
   </si>
   <si>
     <t>COSTELA SUINA KG</t>
+  </si>
+  <si>
+    <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+  </si>
+  <si>
+    <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
+  </si>
+  <si>
+    <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
+  </si>
+  <si>
+    <t>MORTADELA MISTA FRICO 400G MINI</t>
+  </si>
+  <si>
+    <t>MORTADELA MISTA SADIA 400G</t>
+  </si>
+  <si>
+    <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+  </si>
+  <si>
+    <t>BOLINHO DE CARNE SUINA SEARA 270G MOLHO BARBECUE</t>
+  </si>
+  <si>
+    <t>HOT POCKET SADIA 145G X-FRANGO</t>
+  </si>
+  <si>
+    <t>MINI HAMBURGUER SEARA 300G CHURRASCO BOVINO E SUINO</t>
   </si>
 </sst>
 </file>
@@ -75,9 +165,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,8 +203,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,6 +233,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -155,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -172,13 +286,21 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,15 +603,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -508,7 +630,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -520,14 +642,14 @@
         <v>7</v>
       </c>
       <c r="C2" s="3">
-        <v>105470</v>
+        <v>227503</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="7">
-        <v>27.99</v>
+      <c r="F2" s="6">
+        <v>9.99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -535,17 +657,17 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>105468</v>
+        <v>284048</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="7">
-        <v>20.99</v>
+      <c r="F3" s="6">
+        <v>9.99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -553,17 +675,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3">
-        <v>105458</v>
+        <v>336816</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7">
-        <v>21.99</v>
+      <c r="F4" s="6">
+        <v>11.99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -571,17 +693,17 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3">
-        <v>105471</v>
+        <v>104651</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="7">
-        <v>21.99</v>
+      <c r="F5" s="6">
+        <v>7.99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -589,17 +711,17 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3">
-        <v>105435</v>
+        <v>182503</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="7">
-        <v>40.99</v>
+      <c r="F6" s="6">
+        <v>5.99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -607,17 +729,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
-        <v>105062</v>
+        <v>222973</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="7">
-        <v>19.989999999999998</v>
+      <c r="F7" s="6">
+        <v>9.99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -625,21 +747,417 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3">
+        <v>104770</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3">
+        <v>220822</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3">
+        <v>224719</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6">
+        <v>35.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3">
+        <v>298784</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3">
+        <v>108856</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="3">
+        <v>314513</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3">
+        <v>108770</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3">
+        <v>119927</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="3">
+        <v>302029</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3">
+        <v>105470</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3">
+        <v>105468</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="3">
+        <v>105458</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3">
+        <v>105471</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="3">
+        <v>105435</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="3">
+        <v>105062</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="8">
         <v>105433</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
-        <v>19.989999999999998</v>
+      <c r="D24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="3">
+        <v>292399</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3">
+        <v>301962</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="3">
+        <v>158192</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="3">
+        <v>170705</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="3">
+        <v>328607</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="3">
+        <v>116233</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="3">
+        <v>345268</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6">
+        <v>13.49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="257" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>